--- a/docs/cuentas/U-FT-12.010.069_Certificacion_determinacion_cedular_Rentas_de_Trabajo_V.6.1.1VF.xlsx
+++ b/docs/cuentas/U-FT-12.010.069_Certificacion_determinacion_cedular_Rentas_de_Trabajo_V.6.1.1VF.xlsx
@@ -2280,9 +2280,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1428120</xdr:colOff>
+      <xdr:colOff>1427760</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>160920</xdr:rowOff>
+      <xdr:rowOff>160560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2296,7 +2296,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11543760" y="133200"/>
-          <a:ext cx="2942640" cy="1542240"/>
+          <a:ext cx="2942280" cy="1541880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="H17" s="76"/>
       <c r="I17" s="77" t="n">
-        <v>46078</v>
+        <v>46092</v>
       </c>
       <c r="J17" s="78"/>
       <c r="K17" s="2"/>
@@ -6952,7 +6952,7 @@
         <v>48</v>
       </c>
       <c r="C41" s="125" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="D41" s="126"/>
       <c r="E41" s="126"/>
@@ -6984,7 +6984,7 @@
         <v>50</v>
       </c>
       <c r="C42" s="125" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="D42" s="49"/>
       <c r="E42" s="49"/>

--- a/docs/cuentas/U-FT-12.010.069_Certificacion_determinacion_cedular_Rentas_de_Trabajo_V.6.1.1VF.xlsx
+++ b/docs/cuentas/U-FT-12.010.069_Certificacion_determinacion_cedular_Rentas_de_Trabajo_V.6.1.1VF.xlsx
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="142">
   <si>
     <t xml:space="preserve">INSTRUCCIONES DE DILIGENCIAMIENTO </t>
   </si>
@@ -2280,9 +2280,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1427760</xdr:colOff>
+      <xdr:colOff>1427040</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:rowOff>159840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2296,7 +2296,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11543760" y="133200"/>
-          <a:ext cx="2942280" cy="1541880"/>
+          <a:ext cx="2941560" cy="1541160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="H17" s="76"/>
       <c r="I17" s="77" t="n">
-        <v>46092</v>
+        <v>46162</v>
       </c>
       <c r="J17" s="78"/>
       <c r="K17" s="2"/>
@@ -6628,13 +6628,27 @@
     <row r="24" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="90"/>
       <c r="B24" s="91"/>
-      <c r="C24" s="92"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="95"/>
-      <c r="H24" s="95"/>
-      <c r="I24" s="96"/>
+      <c r="C24" s="92" t="n">
+        <v>3065</v>
+      </c>
+      <c r="D24" s="93" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="93" t="n">
+        <v>282</v>
+      </c>
+      <c r="F24" s="94" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="G24" s="95" t="n">
+        <v>45968</v>
+      </c>
+      <c r="H24" s="95" t="n">
+        <v>45991</v>
+      </c>
+      <c r="I24" s="96" t="s">
+        <v>84</v>
+      </c>
       <c r="J24" s="98"/>
     </row>
     <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6683,7 +6697,7 @@
       <c r="E28" s="100"/>
       <c r="F28" s="101" t="n">
         <f aca="false">SUM(F23:F27)</f>
-        <v>54000000</v>
+        <v>72000000</v>
       </c>
       <c r="G28" s="102"/>
       <c r="H28" s="102"/>
@@ -6834,7 +6848,7 @@
       <c r="H36" s="117"/>
       <c r="I36" s="118" t="n">
         <f aca="false">+Datos!F16</f>
-        <v>337500</v>
+        <v>1237500</v>
       </c>
       <c r="J36" s="51"/>
     </row>
@@ -6859,7 +6873,7 @@
       <c r="H37" s="117"/>
       <c r="I37" s="118" t="n">
         <f aca="false">Datos!G16</f>
-        <v>432000</v>
+        <v>1584000</v>
       </c>
       <c r="J37" s="51"/>
     </row>
@@ -6884,7 +6898,7 @@
       <c r="H38" s="117"/>
       <c r="I38" s="118" t="n">
         <f aca="false">Datos!H16</f>
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="J38" s="51"/>
     </row>
@@ -6909,7 +6923,7 @@
       <c r="H39" s="117"/>
       <c r="I39" s="118" t="n">
         <f aca="false">Datos!J16</f>
-        <v>14100</v>
+        <v>51700</v>
       </c>
       <c r="J39" s="51"/>
     </row>
@@ -6926,7 +6940,7 @@
       <c r="H40" s="123"/>
       <c r="I40" s="124" t="n">
         <f aca="false">+SUM(I36:I39)</f>
-        <v>783600</v>
+        <v>2972200</v>
       </c>
       <c r="J40" s="51"/>
       <c r="K40" s="2"/>
@@ -6952,7 +6966,7 @@
         <v>48</v>
       </c>
       <c r="C41" s="125" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="D41" s="126"/>
       <c r="E41" s="126"/>
@@ -6984,7 +6998,7 @@
         <v>50</v>
       </c>
       <c r="C42" s="125" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="D42" s="49"/>
       <c r="E42" s="49"/>
@@ -7275,11 +7289,11 @@
       </c>
       <c r="H52" s="144" t="n">
         <f aca="false">IFERROR(D52/SUM(Datos!$D$11:$D$15)*$I$38,0)</f>
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I52" s="146" t="n">
         <f aca="false">IF($E$45="  SI  ",B52-F52-G52-H52,B52)</f>
-        <v>5980500</v>
+        <v>5953500</v>
       </c>
       <c r="J52" s="51"/>
     </row>
@@ -7287,32 +7301,32 @@
       <c r="A53" s="45"/>
       <c r="B53" s="144" t="n">
         <f aca="false">+IF(C53=0,0,F24/C53)</f>
-        <v>0</v>
+        <v>18000000</v>
       </c>
       <c r="C53" s="145" t="n">
         <f aca="false">+IF(OR(G24="",H24=""),0,((YEAR(H24)-YEAR(G24))*12)+MONTH(H24)-MONTH(G24)+1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" s="144" t="n">
         <f aca="false">+B53*Porcentaje_IBC</f>
-        <v>0</v>
+        <v>7200000</v>
       </c>
       <c r="E53" s="80"/>
       <c r="F53" s="144" t="n">
         <f aca="false">IFERROR(+D53/SUM(Datos!$D$11:$D$15)*I$36,0)</f>
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="G53" s="144" t="n">
         <f aca="false">IFERROR(+D53/SUM(Datos!$D$11:$D$15)*$I$37,0)</f>
-        <v>0</v>
+        <v>1152000</v>
       </c>
       <c r="H53" s="144" t="n">
         <f aca="false">IFERROR(D53/SUM(Datos!$D$11:$D$15)*$I$38,0)</f>
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="I53" s="146" t="n">
         <f aca="false">IF($E$45="  SI  ",B53-F53-G53-H53,B53)</f>
-        <v>0</v>
+        <v>15876000</v>
       </c>
       <c r="J53" s="51"/>
     </row>
@@ -7419,12 +7433,12 @@
       <c r="A57" s="79"/>
       <c r="B57" s="147" t="n">
         <f aca="false">SUM(B52:B56)</f>
-        <v>6750000</v>
+        <v>24750000</v>
       </c>
       <c r="C57" s="148"/>
       <c r="D57" s="147" t="n">
         <f aca="false">IF(SUM(D52:D56)=0,0,Datos!D16)</f>
-        <v>2700000</v>
+        <v>9900000</v>
       </c>
       <c r="E57" s="149"/>
       <c r="F57" s="150"/>
@@ -7432,7 +7446,7 @@
       <c r="H57" s="150"/>
       <c r="I57" s="151" t="n">
         <f aca="false">SUM(I52:I56)</f>
-        <v>5980500</v>
+        <v>21829500</v>
       </c>
       <c r="J57" s="152"/>
       <c r="K57" s="153"/>
@@ -19403,39 +19417,39 @@
       <c r="B12" s="192" t="str">
         <f aca="false">IF(ISBLANK('Certificación Mensual'!E24),"",CONCATENATE('Certificación Mensual'!C24,"-",'Certificación Mensual'!D24,"-",'Certificación Mensual'!E24,"-",YEAR('Certificación Mensual'!G24)
 ))</f>
-        <v/>
+        <v>3065-OSE-282-2025</v>
       </c>
       <c r="C12" s="193" t="n">
         <f aca="false">'Certificación Mensual'!B53</f>
-        <v>0</v>
+        <v>18000000</v>
       </c>
       <c r="D12" s="193" t="n">
         <f aca="false">C12*$B$5</f>
-        <v>0</v>
+        <v>7200000</v>
       </c>
       <c r="E12" s="194" t="n">
         <f aca="false">D12/$B$3</f>
-        <v>0</v>
+        <v>4.11215914055874</v>
       </c>
       <c r="F12" s="144" t="n">
         <f aca="false">D12*$B$6</f>
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="G12" s="144" t="n">
         <f aca="false">IF('Certificación Mensual'!I20="SI","0",D12*$B$7)</f>
-        <v>0</v>
+        <v>1152000</v>
       </c>
       <c r="H12" s="144" t="n">
         <f aca="false">+IF(AND(E12&gt;=$G$3,E12&lt;$H$3),D12*$I$3,IF(AND(E12&gt;=$G$4,E12&lt;$H$4),D12*$I$4,IF(AND(E12&gt;=$G$5,E12&lt;$H$5),D12*$I$5,IF(AND(E12&gt;=$G$6,E12&lt;$H$6),D12*$I$6,IF(AND(E12&gt;=$G$7,E12&lt;$H$7),D12*$I$7,IF(E12&gt;=$G$8,D12*$I$8,IF(E12&gt;=$H$8,Salario_Minimo*25*$I$8,0)))))))</f>
-        <v>0</v>
+        <v>72000</v>
       </c>
-      <c r="I12" s="196" t="n">
+      <c r="I12" s="196" t="str">
         <f aca="false">IF(ISBLANK('certificación mensual'!h22espacios),"0",'Certificación Mensual'!I24)</f>
-        <v>0</v>
+        <v>Riesgo 1</v>
       </c>
       <c r="J12" s="197" t="n">
         <f aca="false">IF(OR(I12="Riesgo 4",I12="Riesgo 5"),0,IFERROR(D12*INDEX($E$3:$E$7,MATCH(I12,$D$3:$D$7,0)),0))</f>
-        <v>0</v>
+        <v>37584</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -19633,32 +19647,32 @@
       <c r="B16" s="198"/>
       <c r="C16" s="199" t="n">
         <f aca="false">IF(SUM(C11:C15)&lt;Salario_Minimo,Salario_Minimo,SUM(C11:C15))</f>
-        <v>6750000</v>
+        <v>24750000</v>
       </c>
       <c r="D16" s="199" t="n">
         <f aca="false">IF(SUM(D11:D15)=0,0,MAX(Salario_Minimo,MIN(SUM(D11:D15),25*Salario_Minimo)))</f>
-        <v>2700000</v>
+        <v>9900000</v>
       </c>
       <c r="E16" s="200" t="n">
         <f aca="false">SUM(E11:E15)</f>
-        <v>1.54205967770953</v>
+        <v>5.65421881826827</v>
       </c>
       <c r="F16" s="199" t="n">
         <f aca="false">IF(SUM(F11:F15)=0,0,MROUND(IF(SUM(F11:F15)&lt;Salario_Minimo*Salud,Salario_Minimo*Salud,IF(SUM(F11:F15)&gt;Salario_Minimo*Salud*25,Salario_Minimo*Salud*25,(SUM(F11:F15)))),100))</f>
-        <v>337500</v>
+        <v>1237500</v>
       </c>
       <c r="G16" s="201" t="n">
         <f aca="false">IF(SUM(G11:G15)=0,0,MROUND(IF('Certificación Mensual'!I18="SI","0",IF(SUM(G11:G15)&lt;Salario_Minimo*Pension,Salario_Minimo*Pension,IF(SUM(G11:G15)&gt;Salario_Minimo*Pension*25,Salario_Minimo*Pension*25,SUM(G11:G15)))),100))</f>
-        <v>432000</v>
+        <v>1584000</v>
       </c>
       <c r="H16" s="201" t="n">
         <f aca="false">MROUND(IF(AND(E16&gt;=$G$3,E16&lt;$H$3),D16*$I$3,IF(AND(E16&gt;=$G$4,E16&lt;$H$4),D16*$I$4,IF(AND(E16&gt;=$G$5,E16&lt;$H$5),D16*$I$5,IF(AND(E16&gt;=$G$6,E16&lt;$H$6),D16*$I$6,IF(AND(E16&gt;=$G$7,E16&lt;$H$7),D16*$I$7,IF(E16&gt;=$G$8,D16*$I$8,IF(E16&gt;=$H$8,Salario_Minimo*25*$I$8,0))))))),100)</f>
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="I16" s="202"/>
       <c r="J16" s="202" t="n">
         <f aca="false" t="array" ref="J16:J16">MROUND(IFERROR(IF(MAX(IF((VALUE(RIGHT($I$11:$I$15,1))&gt;=1)*(VALUE(RIGHT($I$11:$I$15,1))&lt;=3),VALUE(RIGHT($I$11:$I$15,1)),0))=0,0,D16*INDEX($E$3:$E$7,MATCH("Riesgo "&amp;MAX(IF((VALUE(RIGHT($I$11:$I$15,1))&gt;=1)*(VALUE(RIGHT($I$11:$I$15,1))&lt;=3),VALUE(RIGHT($I$11:$I$15,1)),0)),$D$3:$D$7,0))),0),100)</f>
-        <v>14100</v>
+        <v>51700</v>
       </c>
       <c r="K16" s="203"/>
       <c r="L16" s="204"/>
@@ -19711,7 +19725,7 @@
       </c>
       <c r="B18" s="199" t="n">
         <f aca="false">ROUND(C16,0)</f>
-        <v>6750000</v>
+        <v>24750000</v>
       </c>
       <c r="C18" s="206"/>
       <c r="D18" s="154"/>
@@ -19747,7 +19761,7 @@
       </c>
       <c r="B19" s="210" t="n">
         <f aca="false">C16/UVT</f>
-        <v>128.880742353076</v>
+        <v>472.562721961279</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>

--- a/docs/cuentas/U-FT-12.010.069_Certificacion_determinacion_cedular_Rentas_de_Trabajo_V.6.1.1VF.xlsx
+++ b/docs/cuentas/U-FT-12.010.069_Certificacion_determinacion_cedular_Rentas_de_Trabajo_V.6.1.1VF.xlsx
@@ -508,7 +508,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">3065-OSE-141-2025</t>
+    <t xml:space="preserve">3065-OSE-282-2025</t>
   </si>
   <si>
     <t xml:space="preserve">Aporte obligatorio a salud (12,5%)</t>
@@ -2280,9 +2280,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1427040</xdr:colOff>
+      <xdr:colOff>1426680</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>159840</xdr:rowOff>
+      <xdr:rowOff>159480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2296,7 +2296,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11543760" y="133200"/>
-          <a:ext cx="2941560" cy="1541160"/>
+          <a:ext cx="2941200" cy="1540800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="H17" s="76"/>
       <c r="I17" s="77" t="n">
-        <v>46162</v>
+        <v>46224</v>
       </c>
       <c r="J17" s="78"/>
       <c r="K17" s="2"/>
